--- a/apps/super-admin/public/templates/database-backup-template.xlsx
+++ b/apps/super-admin/public/templates/database-backup-template.xlsx
@@ -2,28 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README_BACKUP" sheetId="1" r:id="R098c378db7e04ba4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MANIFEST" sheetId="2" r:id="R56187a05c23f4a9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APP_SETTINGS" sheetId="3" r:id="R93d4e7819ac04c33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USERS" sheetId="4" r:id="Re463d74dd73443c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PARENT_STUDENT_LINKS" sheetId="5" r:id="Rd8ade1e0de5b48a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOPICS" sheetId="6" r:id="R0359c4ef6920413d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATERIALS" sheetId="7" r:id="Rbb4ad1f0681348bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATERIAL_SECTIONS" sheetId="8" r:id="R3d19f2505d294a37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEARNING_OBJECTIVES" sheetId="9" r:id="Rad84e6fd19a347cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TKAD_TIPS" sheetId="10" r:id="R52a4beb300e44d7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BLUEPRINTS" sheetId="11" r:id="R8778807823c24814"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTIONS" sheetId="12" r:id="Re262c62bf03f48e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTION_OPTIONS" sheetId="13" r:id="R6156516ea5f3493f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRYOUTS" sheetId="14" r:id="Rfe08d8e2e5bf4d63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRYOUT_QUESTIONS" sheetId="15" r:id="R549f16fdb55149ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATTEMPTS" sheetId="16" r:id="R125b247d068f400c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATTEMPT_ANSWERS" sheetId="17" r:id="R79a2ad877c8541e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRACTICE_ATTEMPTS" sheetId="18" r:id="Rd4844903833146b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRACTICE_ANSWERS" sheetId="19" r:id="R8841c202f3f24c11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRYOUT_INCIDENTS" sheetId="20" r:id="Re113337dd6254949"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTIFICATIONS" sheetId="21" r:id="Rb3827ec615364e64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LONG_TEXT" sheetId="22" r:id="R05247deb6061476b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README_BACKUP" sheetId="1" r:id="R6cc568dc37134fb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MANIFEST" sheetId="2" r:id="R8853a8f99c914e2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APP_SETTINGS" sheetId="3" r:id="Rbecebfab0d204089"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USERS" sheetId="4" r:id="Re71f34cf5ec141b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PARENT_STUDENT_LINKS" sheetId="5" r:id="Rb34ccc9c815949ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOPICS" sheetId="6" r:id="R1c974d94edf94a27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATERIALS" sheetId="7" r:id="Ra1c5502226d14e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATERIAL_SECTIONS" sheetId="8" r:id="R233b02494b3042b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEARNING_OBJECTIVES" sheetId="9" r:id="Re2225feabb104e3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TKAD_TIPS" sheetId="10" r:id="R6d4f826409004b1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BLUEPRINTS" sheetId="11" r:id="R48395851a67c4fe7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTIONS" sheetId="12" r:id="R88319e4033af4123"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTION_OPTIONS" sheetId="13" r:id="R13947c9c40a24e92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRYOUTS" sheetId="14" r:id="R89c1ff6a0d6e4268"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRYOUT_QUESTIONS" sheetId="15" r:id="R05202bcf7d354b6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATTEMPTS" sheetId="16" r:id="Reedf84d959f94b96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATTEMPT_ANSWERS" sheetId="17" r:id="R640202bec4654ab9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRACTICE_ATTEMPTS" sheetId="18" r:id="R4cd75b9a87a64133"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRACTICE_ANSWERS" sheetId="19" r:id="Rbbae02b352a74f54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRYOUT_INCIDENTS" sheetId="20" r:id="R1bc1d6c85445429a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LONG_TEXT" sheetId="21" r:id="Rf0dac013a3254e24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -51,7 +50,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -73,16 +72,6 @@
         <x:fgColor rgb="FFF57C00"/>
       </x:patternFill>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF57C00"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFECEFF1"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -91,7 +80,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -147,23 +136,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -322,7 +294,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -346,7 +318,7 @@
         <x:v>appVersion</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
-        <x:v>18.1</x:v>
+        <x:v>16.1-backup-only</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -378,7 +350,7 @@
         <x:v>sheetCount</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -406,11 +378,19 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="36" t="str">
+      <x:c r="A11" s="13" t="str">
         <x:v>TEKS PANJANG</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
         <x:v>Nilai lebih dari 32.000 karakter disimpan utuh dalam sheet LONG_TEXT.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>CATATAN</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>Versi ini tidak memuat sheet NOTIFICATIONS karena fitur notifikasi belum diimplementasikan.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -936,7 +916,7 @@
         <x:v>APP_SETTINGS</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>APP_SETTINGS</x:v>
+        <x:v>AppSetting</x:v>
       </x:c>
       <x:c r="D2" s="14" t="n">
         <x:v>0</x:v>
@@ -953,7 +933,7 @@
         <x:v>USERS</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
-        <x:v>USERS</x:v>
+        <x:v>User</x:v>
       </x:c>
       <x:c r="D3" s="14" t="n">
         <x:v>0</x:v>
@@ -970,7 +950,7 @@
         <x:v>PARENT_STUDENT_LINKS</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>PARENT_STUDENT_LINKS</x:v>
+        <x:v>ParentStudentLink</x:v>
       </x:c>
       <x:c r="D4" s="14" t="n">
         <x:v>0</x:v>
@@ -987,7 +967,7 @@
         <x:v>TOPICS</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>TOPICS</x:v>
+        <x:v>Topic</x:v>
       </x:c>
       <x:c r="D5" s="14" t="n">
         <x:v>0</x:v>
@@ -1004,7 +984,7 @@
         <x:v>MATERIALS</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
-        <x:v>MATERIALS</x:v>
+        <x:v>Material</x:v>
       </x:c>
       <x:c r="D6" s="14" t="n">
         <x:v>0</x:v>
@@ -1021,7 +1001,7 @@
         <x:v>MATERIAL_SECTIONS</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
-        <x:v>MATERIAL_SECTIONS</x:v>
+        <x:v>MaterialSection</x:v>
       </x:c>
       <x:c r="D7" s="14" t="n">
         <x:v>0</x:v>
@@ -1038,7 +1018,7 @@
         <x:v>LEARNING_OBJECTIVES</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
-        <x:v>LEARNING_OBJECTIVES</x:v>
+        <x:v>LearningObjective</x:v>
       </x:c>
       <x:c r="D8" s="14" t="n">
         <x:v>0</x:v>
@@ -1055,7 +1035,7 @@
         <x:v>TKAD_TIPS</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>TKAD_TIPS</x:v>
+        <x:v>TkadTip</x:v>
       </x:c>
       <x:c r="D9" s="14" t="n">
         <x:v>0</x:v>
@@ -1072,7 +1052,7 @@
         <x:v>BLUEPRINTS</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
-        <x:v>BLUEPRINTS</x:v>
+        <x:v>Blueprint</x:v>
       </x:c>
       <x:c r="D10" s="14" t="n">
         <x:v>0</x:v>
@@ -1089,7 +1069,7 @@
         <x:v>QUESTIONS</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>QUESTIONS</x:v>
+        <x:v>Question</x:v>
       </x:c>
       <x:c r="D11" s="14" t="n">
         <x:v>0</x:v>
@@ -1106,7 +1086,7 @@
         <x:v>QUESTION_OPTIONS</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
-        <x:v>QUESTION_OPTIONS</x:v>
+        <x:v>QuestionOption</x:v>
       </x:c>
       <x:c r="D12" s="14" t="n">
         <x:v>0</x:v>
@@ -1123,7 +1103,7 @@
         <x:v>TRYOUTS</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>TRYOUTS</x:v>
+        <x:v>Tryout</x:v>
       </x:c>
       <x:c r="D13" s="14" t="n">
         <x:v>0</x:v>
@@ -1140,7 +1120,7 @@
         <x:v>TRYOUT_QUESTIONS</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>TRYOUT_QUESTIONS</x:v>
+        <x:v>TryoutQuestion</x:v>
       </x:c>
       <x:c r="D14" s="14" t="n">
         <x:v>0</x:v>
@@ -1157,7 +1137,7 @@
         <x:v>ATTEMPTS</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>ATTEMPTS</x:v>
+        <x:v>Attempt</x:v>
       </x:c>
       <x:c r="D15" s="14" t="n">
         <x:v>0</x:v>
@@ -1174,7 +1154,7 @@
         <x:v>ATTEMPT_ANSWERS</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>ATTEMPT_ANSWERS</x:v>
+        <x:v>AttemptAnswer</x:v>
       </x:c>
       <x:c r="D16" s="14" t="n">
         <x:v>0</x:v>
@@ -1191,7 +1171,7 @@
         <x:v>PRACTICE_ATTEMPTS</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
-        <x:v>PRACTICE_ATTEMPTS</x:v>
+        <x:v>PracticeAttempt</x:v>
       </x:c>
       <x:c r="D17" s="14" t="n">
         <x:v>0</x:v>
@@ -1208,7 +1188,7 @@
         <x:v>PRACTICE_ANSWERS</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>PRACTICE_ANSWERS</x:v>
+        <x:v>PracticeAnswer</x:v>
       </x:c>
       <x:c r="D18" s="14" t="n">
         <x:v>0</x:v>
@@ -1225,30 +1205,13 @@
         <x:v>TRYOUT_INCIDENTS</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>TRYOUT_INCIDENTS</x:v>
+        <x:v>TryoutIncident</x:v>
       </x:c>
       <x:c r="D19" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
         <x:v>Log audit insiden selama tryout.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="14" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B20" s="14" t="str">
-        <x:v>NOTIFICATIONS</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="str">
-        <x:v>NOTIFICATIONS</x:v>
-      </x:c>
-      <x:c r="D20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="str">
-        <x:v>Pusat notifikasi seluruh pengguna.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1301,84 +1264,31 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="25" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="B1" s="25" t="str">
-        <x:v>recipientId</x:v>
-      </x:c>
-      <x:c r="C1" s="25" t="str">
-        <x:v>senderId</x:v>
-      </x:c>
-      <x:c r="D1" s="25" t="str">
-        <x:v>type</x:v>
-      </x:c>
-      <x:c r="E1" s="25" t="str">
-        <x:v>title</x:v>
-      </x:c>
-      <x:c r="F1" s="25" t="str">
-        <x:v>message</x:v>
-      </x:c>
-      <x:c r="G1" s="25" t="str">
-        <x:v>link</x:v>
-      </x:c>
-      <x:c r="H1" s="25" t="str">
-        <x:v>isRead</x:v>
-      </x:c>
-      <x:c r="I1" s="25" t="str">
-        <x:v>readAt</x:v>
-      </x:c>
-      <x:c r="J1" s="25" t="str">
-        <x:v>createdAt</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
     <x:col min="1" max="1" width="36" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="70" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="33" t="str">
+    <x:row r="1">
+      <x:c r="A1" s="20" t="str">
         <x:v>reference</x:v>
       </x:c>
-      <x:c r="B1" s="33" t="str">
+      <x:c r="B1" s="20" t="str">
         <x:v>sourceSheet</x:v>
       </x:c>
-      <x:c r="C1" s="33" t="str">
+      <x:c r="C1" s="20" t="str">
         <x:v>sourceRow</x:v>
       </x:c>
-      <x:c r="D1" s="33" t="str">
+      <x:c r="D1" s="20" t="str">
         <x:v>sourceColumn</x:v>
       </x:c>
-      <x:c r="E1" s="33" t="str">
+      <x:c r="E1" s="20" t="str">
         <x:v>chunkNo</x:v>
       </x:c>
-      <x:c r="F1" s="33" t="str">
+      <x:c r="F1" s="20" t="str">
         <x:v>content</x:v>
       </x:c>
     </x:row>
